--- a/templates/invoice_template_v2.xlsx
+++ b/templates/invoice_template_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Проекты\Агент Авто Континент\01_БОТ_АКТУАЛЬНЫЙ\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23365E3C-8774-425C-BE16-799BA6771F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB5A59AB-5018-413D-8C46-A69187471A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,7 +167,7 @@
     <t>{{ДИРЕКТОР}}</t>
   </si>
   <si>
-    <t>{{КОМПАНИЯ}}, ИНН: {{КОМПАНИЯ_ИНН}}, ИНН РФ: {{КОМПАНИЯ_ИНН_РФ}}, ОКПО: {{КОМПАНИЯ_ОКПО}}, {{КОМПАНИЯ_АДРЕС}}</t>
+    <t>{{КОМПАНИЯ}}, ИНН: {{КОМПАНИЯ_ИНН}}, ОКПО: {{КОМПАНИЯ_ОКПО}}, {{КОМПАНИЯ_АДРЕС}}</t>
   </si>
 </sst>
 </file>
@@ -583,7 +583,69 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -602,75 +664,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -700,7 +700,7 @@
     <xdr:ext cx="1768048" cy="1544504"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr descr="stamp" id="2" name="image2.png" title="Изображение">
+        <xdr:cNvPr id="2" name="image2.png" descr="stamp" title="Изображение">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
@@ -730,15 +730,15 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>2538</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>57572</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>111123</xdr:rowOff>
+      <xdr:rowOff>1056</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1205130" cy="607695"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr descr="signature" id="3" name="image1.png" title="Изображение">
+        <xdr:cNvPr id="3" name="image1.png" descr="signature" title="Изображение">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
@@ -755,7 +755,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2207258" y="6136003"/>
+          <a:off x="2030305" y="5555189"/>
           <a:ext cx="1205130" cy="607695"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1033,441 +1033,441 @@
     </row>
     <row r="2" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
-      <c r="U2" s="39" t="s">
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="41"/>
+      <c r="S2" s="41"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="V2" s="40"/>
-      <c r="W2" s="40"/>
-      <c r="X2" s="41"/>
-      <c r="Y2" s="42" t="s">
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="Z2" s="38"/>
-      <c r="AA2" s="38"/>
-      <c r="AB2" s="38"/>
-      <c r="AC2" s="38"/>
-      <c r="AD2" s="38"/>
-      <c r="AE2" s="38"/>
-      <c r="AF2" s="38"/>
-      <c r="AG2" s="38"/>
-      <c r="AH2" s="38"/>
-      <c r="AI2" s="38"/>
-      <c r="AJ2" s="38"/>
-      <c r="AK2" s="38"/>
-      <c r="AL2" s="43"/>
+      <c r="Z2" s="41"/>
+      <c r="AA2" s="41"/>
+      <c r="AB2" s="41"/>
+      <c r="AC2" s="41"/>
+      <c r="AD2" s="41"/>
+      <c r="AE2" s="41"/>
+      <c r="AF2" s="41"/>
+      <c r="AG2" s="41"/>
+      <c r="AH2" s="41"/>
+      <c r="AI2" s="41"/>
+      <c r="AJ2" s="41"/>
+      <c r="AK2" s="41"/>
+      <c r="AL2" s="42"/>
     </row>
     <row r="3" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="46"/>
-      <c r="U3" s="47" t="s">
+      <c r="B3" s="45"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
+      <c r="S3" s="37"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="V3" s="46"/>
-      <c r="W3" s="46"/>
-      <c r="X3" s="48"/>
-      <c r="Y3" s="49" t="s">
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="31"/>
+      <c r="Y3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="Z3" s="45"/>
-      <c r="AA3" s="45"/>
-      <c r="AB3" s="45"/>
-      <c r="AC3" s="45"/>
-      <c r="AD3" s="45"/>
-      <c r="AE3" s="45"/>
-      <c r="AF3" s="45"/>
-      <c r="AG3" s="45"/>
-      <c r="AH3" s="45"/>
-      <c r="AI3" s="45"/>
-      <c r="AJ3" s="45"/>
-      <c r="AK3" s="45"/>
-      <c r="AL3" s="50"/>
+      <c r="Z3" s="37"/>
+      <c r="AA3" s="37"/>
+      <c r="AB3" s="37"/>
+      <c r="AC3" s="37"/>
+      <c r="AD3" s="37"/>
+      <c r="AE3" s="37"/>
+      <c r="AF3" s="37"/>
+      <c r="AG3" s="37"/>
+      <c r="AH3" s="37"/>
+      <c r="AI3" s="37"/>
+      <c r="AJ3" s="37"/>
+      <c r="AK3" s="37"/>
+      <c r="AL3" s="36"/>
     </row>
     <row r="4" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="52"/>
-      <c r="Q4" s="52"/>
-      <c r="R4" s="52"/>
-      <c r="S4" s="52"/>
-      <c r="T4" s="52"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="38"/>
       <c r="U4" s="53"/>
-      <c r="V4" s="46"/>
-      <c r="W4" s="46"/>
-      <c r="X4" s="48"/>
-      <c r="Y4" s="52"/>
-      <c r="Z4" s="52"/>
-      <c r="AA4" s="52"/>
-      <c r="AB4" s="52"/>
-      <c r="AC4" s="52"/>
-      <c r="AD4" s="52"/>
-      <c r="AE4" s="52"/>
-      <c r="AF4" s="52"/>
-      <c r="AG4" s="52"/>
-      <c r="AH4" s="52"/>
-      <c r="AI4" s="52"/>
-      <c r="AJ4" s="52"/>
-      <c r="AK4" s="52"/>
-      <c r="AL4" s="54"/>
+      <c r="V4" s="30"/>
+      <c r="W4" s="30"/>
+      <c r="X4" s="31"/>
+      <c r="Y4" s="38"/>
+      <c r="Z4" s="38"/>
+      <c r="AA4" s="38"/>
+      <c r="AB4" s="38"/>
+      <c r="AC4" s="38"/>
+      <c r="AD4" s="38"/>
+      <c r="AE4" s="38"/>
+      <c r="AF4" s="38"/>
+      <c r="AG4" s="38"/>
+      <c r="AH4" s="38"/>
+      <c r="AI4" s="38"/>
+      <c r="AJ4" s="38"/>
+      <c r="AK4" s="38"/>
+      <c r="AL4" s="39"/>
     </row>
     <row r="5" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="38"/>
-      <c r="T5" s="38"/>
-      <c r="U5" s="39" t="s">
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="41"/>
+      <c r="R5" s="41"/>
+      <c r="S5" s="41"/>
+      <c r="T5" s="41"/>
+      <c r="U5" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="V5" s="40"/>
-      <c r="W5" s="40"/>
-      <c r="X5" s="41"/>
-      <c r="Y5" s="55" t="s">
+      <c r="V5" s="27"/>
+      <c r="W5" s="27"/>
+      <c r="X5" s="28"/>
+      <c r="Y5" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="Z5" s="38"/>
-      <c r="AA5" s="38"/>
-      <c r="AB5" s="38"/>
-      <c r="AC5" s="38"/>
-      <c r="AD5" s="38"/>
-      <c r="AE5" s="38"/>
-      <c r="AF5" s="38"/>
-      <c r="AG5" s="38"/>
-      <c r="AH5" s="38"/>
-      <c r="AI5" s="38"/>
-      <c r="AJ5" s="38"/>
-      <c r="AK5" s="38"/>
-      <c r="AL5" s="43"/>
+      <c r="Z5" s="41"/>
+      <c r="AA5" s="41"/>
+      <c r="AB5" s="41"/>
+      <c r="AC5" s="41"/>
+      <c r="AD5" s="41"/>
+      <c r="AE5" s="41"/>
+      <c r="AF5" s="41"/>
+      <c r="AG5" s="41"/>
+      <c r="AH5" s="41"/>
+      <c r="AI5" s="41"/>
+      <c r="AJ5" s="41"/>
+      <c r="AK5" s="41"/>
+      <c r="AL5" s="42"/>
     </row>
     <row r="6" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
-      <c r="B6" s="44"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="45"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="45"/>
-      <c r="P6" s="45"/>
-      <c r="Q6" s="45"/>
-      <c r="R6" s="45"/>
-      <c r="S6" s="45"/>
-      <c r="T6" s="46"/>
-      <c r="U6" s="47" t="s">
+      <c r="B6" s="45"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="37"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="37"/>
+      <c r="O6" s="37"/>
+      <c r="P6" s="37"/>
+      <c r="Q6" s="37"/>
+      <c r="R6" s="37"/>
+      <c r="S6" s="37"/>
+      <c r="T6" s="30"/>
+      <c r="U6" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="46"/>
-      <c r="W6" s="46"/>
-      <c r="X6" s="48"/>
-      <c r="Y6" s="49" t="s">
+      <c r="V6" s="30"/>
+      <c r="W6" s="30"/>
+      <c r="X6" s="31"/>
+      <c r="Y6" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="Z6" s="45"/>
-      <c r="AA6" s="45"/>
-      <c r="AB6" s="45"/>
-      <c r="AC6" s="45"/>
-      <c r="AD6" s="45"/>
-      <c r="AE6" s="45"/>
-      <c r="AF6" s="45"/>
-      <c r="AG6" s="45"/>
-      <c r="AH6" s="45"/>
-      <c r="AI6" s="45"/>
-      <c r="AJ6" s="45"/>
-      <c r="AK6" s="45"/>
-      <c r="AL6" s="50"/>
+      <c r="Z6" s="37"/>
+      <c r="AA6" s="37"/>
+      <c r="AB6" s="37"/>
+      <c r="AC6" s="37"/>
+      <c r="AD6" s="37"/>
+      <c r="AE6" s="37"/>
+      <c r="AF6" s="37"/>
+      <c r="AG6" s="37"/>
+      <c r="AH6" s="37"/>
+      <c r="AI6" s="37"/>
+      <c r="AJ6" s="37"/>
+      <c r="AK6" s="37"/>
+      <c r="AL6" s="36"/>
     </row>
     <row r="7" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-      <c r="B7" s="56" t="s">
+      <c r="B7" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="46"/>
-      <c r="N7" s="46"/>
-      <c r="O7" s="46"/>
-      <c r="P7" s="46"/>
-      <c r="Q7" s="46"/>
-      <c r="R7" s="46"/>
-      <c r="S7" s="46"/>
-      <c r="T7" s="46"/>
-      <c r="U7" s="57"/>
-      <c r="V7" s="58"/>
-      <c r="W7" s="58"/>
-      <c r="X7" s="59"/>
-      <c r="Y7" s="52"/>
-      <c r="Z7" s="52"/>
-      <c r="AA7" s="52"/>
-      <c r="AB7" s="52"/>
-      <c r="AC7" s="52"/>
-      <c r="AD7" s="52"/>
-      <c r="AE7" s="52"/>
-      <c r="AF7" s="52"/>
-      <c r="AG7" s="52"/>
-      <c r="AH7" s="52"/>
-      <c r="AI7" s="52"/>
-      <c r="AJ7" s="52"/>
-      <c r="AK7" s="52"/>
-      <c r="AL7" s="54"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="30"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="30"/>
+      <c r="U7" s="32"/>
+      <c r="V7" s="33"/>
+      <c r="W7" s="33"/>
+      <c r="X7" s="34"/>
+      <c r="Y7" s="38"/>
+      <c r="Z7" s="38"/>
+      <c r="AA7" s="38"/>
+      <c r="AB7" s="38"/>
+      <c r="AC7" s="38"/>
+      <c r="AD7" s="38"/>
+      <c r="AE7" s="38"/>
+      <c r="AF7" s="38"/>
+      <c r="AG7" s="38"/>
+      <c r="AH7" s="38"/>
+      <c r="AI7" s="38"/>
+      <c r="AJ7" s="38"/>
+      <c r="AK7" s="38"/>
+      <c r="AL7" s="39"/>
     </row>
     <row r="8" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="40"/>
-      <c r="D8" s="60" t="s">
+      <c r="C8" s="27"/>
+      <c r="D8" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="61" t="s">
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="L8" s="40"/>
-      <c r="M8" s="62"/>
-      <c r="N8" s="40"/>
-      <c r="O8" s="40"/>
-      <c r="P8" s="40"/>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="40"/>
-      <c r="S8" s="40"/>
-      <c r="T8" s="41"/>
-      <c r="U8" s="63" t="s">
+      <c r="L8" s="27"/>
+      <c r="M8" s="51"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="27"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="28"/>
+      <c r="U8" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="V8" s="46"/>
-      <c r="W8" s="46"/>
-      <c r="X8" s="50"/>
-      <c r="Y8" s="64" t="s">
+      <c r="V8" s="30"/>
+      <c r="W8" s="30"/>
+      <c r="X8" s="36"/>
+      <c r="Y8" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="Z8" s="38"/>
-      <c r="AA8" s="38"/>
-      <c r="AB8" s="38"/>
-      <c r="AC8" s="38"/>
-      <c r="AD8" s="38"/>
-      <c r="AE8" s="38"/>
-      <c r="AF8" s="38"/>
-      <c r="AG8" s="38"/>
-      <c r="AH8" s="38"/>
-      <c r="AI8" s="38"/>
-      <c r="AJ8" s="38"/>
-      <c r="AK8" s="38"/>
-      <c r="AL8" s="43"/>
+      <c r="Z8" s="41"/>
+      <c r="AA8" s="41"/>
+      <c r="AB8" s="41"/>
+      <c r="AC8" s="41"/>
+      <c r="AD8" s="41"/>
+      <c r="AE8" s="41"/>
+      <c r="AF8" s="41"/>
+      <c r="AG8" s="41"/>
+      <c r="AH8" s="41"/>
+      <c r="AI8" s="41"/>
+      <c r="AJ8" s="41"/>
+      <c r="AK8" s="41"/>
+      <c r="AL8" s="42"/>
     </row>
     <row r="9" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="65" t="s">
+      <c r="B9" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="46"/>
-      <c r="N9" s="46"/>
-      <c r="O9" s="46"/>
-      <c r="P9" s="46"/>
-      <c r="Q9" s="46"/>
-      <c r="R9" s="46"/>
-      <c r="S9" s="46"/>
-      <c r="T9" s="48"/>
-      <c r="U9" s="46"/>
-      <c r="V9" s="45"/>
-      <c r="W9" s="45"/>
-      <c r="X9" s="50"/>
-      <c r="Y9" s="44"/>
-      <c r="Z9" s="45"/>
-      <c r="AA9" s="45"/>
-      <c r="AB9" s="45"/>
-      <c r="AC9" s="45"/>
-      <c r="AD9" s="45"/>
-      <c r="AE9" s="45"/>
-      <c r="AF9" s="45"/>
-      <c r="AG9" s="45"/>
-      <c r="AH9" s="45"/>
-      <c r="AI9" s="45"/>
-      <c r="AJ9" s="45"/>
-      <c r="AK9" s="45"/>
-      <c r="AL9" s="50"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="30"/>
+      <c r="R9" s="30"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="30"/>
+      <c r="V9" s="37"/>
+      <c r="W9" s="37"/>
+      <c r="X9" s="36"/>
+      <c r="Y9" s="45"/>
+      <c r="Z9" s="37"/>
+      <c r="AA9" s="37"/>
+      <c r="AB9" s="37"/>
+      <c r="AC9" s="37"/>
+      <c r="AD9" s="37"/>
+      <c r="AE9" s="37"/>
+      <c r="AF9" s="37"/>
+      <c r="AG9" s="37"/>
+      <c r="AH9" s="37"/>
+      <c r="AI9" s="37"/>
+      <c r="AJ9" s="37"/>
+      <c r="AK9" s="37"/>
+      <c r="AL9" s="36"/>
     </row>
     <row r="10" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="53"/>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="66"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="66"/>
-      <c r="J10" s="66"/>
-      <c r="K10" s="66"/>
-      <c r="L10" s="66"/>
-      <c r="M10" s="66"/>
-      <c r="N10" s="66"/>
-      <c r="O10" s="66"/>
-      <c r="P10" s="66"/>
-      <c r="Q10" s="66"/>
-      <c r="R10" s="66"/>
-      <c r="S10" s="66"/>
-      <c r="T10" s="67"/>
-      <c r="U10" s="46"/>
-      <c r="V10" s="45"/>
-      <c r="W10" s="45"/>
-      <c r="X10" s="50"/>
-      <c r="Y10" s="44"/>
-      <c r="Z10" s="45"/>
-      <c r="AA10" s="45"/>
-      <c r="AB10" s="45"/>
-      <c r="AC10" s="45"/>
-      <c r="AD10" s="45"/>
-      <c r="AE10" s="45"/>
-      <c r="AF10" s="45"/>
-      <c r="AG10" s="45"/>
-      <c r="AH10" s="45"/>
-      <c r="AI10" s="45"/>
-      <c r="AJ10" s="45"/>
-      <c r="AK10" s="45"/>
-      <c r="AL10" s="50"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="54"/>
+      <c r="N10" s="54"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="54"/>
+      <c r="Q10" s="54"/>
+      <c r="R10" s="54"/>
+      <c r="S10" s="54"/>
+      <c r="T10" s="55"/>
+      <c r="U10" s="30"/>
+      <c r="V10" s="37"/>
+      <c r="W10" s="37"/>
+      <c r="X10" s="36"/>
+      <c r="Y10" s="45"/>
+      <c r="Z10" s="37"/>
+      <c r="AA10" s="37"/>
+      <c r="AB10" s="37"/>
+      <c r="AC10" s="37"/>
+      <c r="AD10" s="37"/>
+      <c r="AE10" s="37"/>
+      <c r="AF10" s="37"/>
+      <c r="AG10" s="37"/>
+      <c r="AH10" s="37"/>
+      <c r="AI10" s="37"/>
+      <c r="AJ10" s="37"/>
+      <c r="AK10" s="37"/>
+      <c r="AL10" s="36"/>
     </row>
     <row r="11" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="68" t="s">
+      <c r="B11" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="58"/>
-      <c r="K11" s="58"/>
-      <c r="L11" s="58"/>
-      <c r="M11" s="58"/>
-      <c r="N11" s="58"/>
-      <c r="O11" s="58"/>
-      <c r="P11" s="58"/>
-      <c r="Q11" s="58"/>
-      <c r="R11" s="58"/>
-      <c r="S11" s="58"/>
-      <c r="T11" s="59"/>
-      <c r="U11" s="52"/>
-      <c r="V11" s="52"/>
-      <c r="W11" s="52"/>
-      <c r="X11" s="54"/>
-      <c r="Y11" s="69"/>
-      <c r="Z11" s="52"/>
-      <c r="AA11" s="52"/>
-      <c r="AB11" s="52"/>
-      <c r="AC11" s="52"/>
-      <c r="AD11" s="52"/>
-      <c r="AE11" s="52"/>
-      <c r="AF11" s="52"/>
-      <c r="AG11" s="52"/>
-      <c r="AH11" s="52"/>
-      <c r="AI11" s="52"/>
-      <c r="AJ11" s="52"/>
-      <c r="AK11" s="52"/>
-      <c r="AL11" s="54"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="33"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="33"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="33"/>
+      <c r="Q11" s="33"/>
+      <c r="R11" s="33"/>
+      <c r="S11" s="33"/>
+      <c r="T11" s="34"/>
+      <c r="U11" s="38"/>
+      <c r="V11" s="38"/>
+      <c r="W11" s="38"/>
+      <c r="X11" s="39"/>
+      <c r="Y11" s="46"/>
+      <c r="Z11" s="38"/>
+      <c r="AA11" s="38"/>
+      <c r="AB11" s="38"/>
+      <c r="AC11" s="38"/>
+      <c r="AD11" s="38"/>
+      <c r="AE11" s="38"/>
+      <c r="AF11" s="38"/>
+      <c r="AG11" s="38"/>
+      <c r="AH11" s="38"/>
+      <c r="AI11" s="38"/>
+      <c r="AJ11" s="38"/>
+      <c r="AK11" s="38"/>
+      <c r="AL11" s="39"/>
     </row>
     <row r="12" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
@@ -1511,125 +1511,125 @@
     </row>
     <row r="13" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
-      <c r="M13" s="28"/>
-      <c r="N13" s="28"/>
-      <c r="O13" s="28"/>
-      <c r="P13" s="28"/>
-      <c r="Q13" s="28"/>
-      <c r="R13" s="28"/>
-      <c r="S13" s="28"/>
-      <c r="T13" s="28"/>
-      <c r="U13" s="28"/>
-      <c r="V13" s="28"/>
-      <c r="W13" s="28"/>
-      <c r="X13" s="28"/>
-      <c r="Y13" s="28"/>
-      <c r="Z13" s="28"/>
-      <c r="AA13" s="28"/>
-      <c r="AB13" s="28"/>
-      <c r="AC13" s="28"/>
-      <c r="AD13" s="28"/>
-      <c r="AE13" s="28"/>
-      <c r="AF13" s="28"/>
-      <c r="AG13" s="28"/>
-      <c r="AH13" s="28"/>
-      <c r="AI13" s="28"/>
-      <c r="AJ13" s="28"/>
-      <c r="AK13" s="28"/>
-      <c r="AL13" s="28"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="60"/>
+      <c r="K13" s="60"/>
+      <c r="L13" s="60"/>
+      <c r="M13" s="60"/>
+      <c r="N13" s="60"/>
+      <c r="O13" s="60"/>
+      <c r="P13" s="60"/>
+      <c r="Q13" s="60"/>
+      <c r="R13" s="60"/>
+      <c r="S13" s="60"/>
+      <c r="T13" s="60"/>
+      <c r="U13" s="60"/>
+      <c r="V13" s="60"/>
+      <c r="W13" s="60"/>
+      <c r="X13" s="60"/>
+      <c r="Y13" s="60"/>
+      <c r="Z13" s="60"/>
+      <c r="AA13" s="60"/>
+      <c r="AB13" s="60"/>
+      <c r="AC13" s="60"/>
+      <c r="AD13" s="60"/>
+      <c r="AE13" s="60"/>
+      <c r="AF13" s="60"/>
+      <c r="AG13" s="60"/>
+      <c r="AH13" s="60"/>
+      <c r="AI13" s="60"/>
+      <c r="AJ13" s="60"/>
+      <c r="AK13" s="60"/>
+      <c r="AL13" s="60"/>
     </row>
     <row r="14" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="28"/>
-      <c r="M14" s="28"/>
-      <c r="N14" s="28"/>
-      <c r="O14" s="28"/>
-      <c r="P14" s="28"/>
-      <c r="Q14" s="28"/>
-      <c r="R14" s="28"/>
-      <c r="S14" s="28"/>
-      <c r="T14" s="28"/>
-      <c r="U14" s="28"/>
-      <c r="V14" s="28"/>
-      <c r="W14" s="28"/>
-      <c r="X14" s="28"/>
-      <c r="Y14" s="28"/>
-      <c r="Z14" s="28"/>
-      <c r="AA14" s="28"/>
-      <c r="AB14" s="28"/>
-      <c r="AC14" s="28"/>
-      <c r="AD14" s="28"/>
-      <c r="AE14" s="28"/>
-      <c r="AF14" s="28"/>
-      <c r="AG14" s="28"/>
-      <c r="AH14" s="28"/>
-      <c r="AI14" s="28"/>
-      <c r="AJ14" s="28"/>
-      <c r="AK14" s="28"/>
-      <c r="AL14" s="28"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="60"/>
+      <c r="L14" s="60"/>
+      <c r="M14" s="60"/>
+      <c r="N14" s="60"/>
+      <c r="O14" s="60"/>
+      <c r="P14" s="60"/>
+      <c r="Q14" s="60"/>
+      <c r="R14" s="60"/>
+      <c r="S14" s="60"/>
+      <c r="T14" s="60"/>
+      <c r="U14" s="60"/>
+      <c r="V14" s="60"/>
+      <c r="W14" s="60"/>
+      <c r="X14" s="60"/>
+      <c r="Y14" s="60"/>
+      <c r="Z14" s="60"/>
+      <c r="AA14" s="60"/>
+      <c r="AB14" s="60"/>
+      <c r="AC14" s="60"/>
+      <c r="AD14" s="60"/>
+      <c r="AE14" s="60"/>
+      <c r="AF14" s="60"/>
+      <c r="AG14" s="60"/>
+      <c r="AH14" s="60"/>
+      <c r="AI14" s="60"/>
+      <c r="AJ14" s="60"/>
+      <c r="AK14" s="60"/>
+      <c r="AL14" s="60"/>
     </row>
     <row r="15" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="30"/>
-      <c r="P15" s="30"/>
-      <c r="Q15" s="30"/>
-      <c r="R15" s="30"/>
-      <c r="S15" s="30"/>
-      <c r="T15" s="30"/>
-      <c r="U15" s="30"/>
-      <c r="V15" s="30"/>
-      <c r="W15" s="30"/>
-      <c r="X15" s="30"/>
-      <c r="Y15" s="30"/>
-      <c r="Z15" s="30"/>
-      <c r="AA15" s="30"/>
-      <c r="AB15" s="30"/>
-      <c r="AC15" s="30"/>
-      <c r="AD15" s="30"/>
-      <c r="AE15" s="30"/>
-      <c r="AF15" s="30"/>
-      <c r="AG15" s="30"/>
-      <c r="AH15" s="30"/>
-      <c r="AI15" s="30"/>
-      <c r="AJ15" s="30"/>
-      <c r="AK15" s="30"/>
-      <c r="AL15" s="30"/>
+      <c r="B15" s="61"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="62"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="62"/>
+      <c r="M15" s="62"/>
+      <c r="N15" s="62"/>
+      <c r="O15" s="62"/>
+      <c r="P15" s="62"/>
+      <c r="Q15" s="62"/>
+      <c r="R15" s="62"/>
+      <c r="S15" s="62"/>
+      <c r="T15" s="62"/>
+      <c r="U15" s="62"/>
+      <c r="V15" s="62"/>
+      <c r="W15" s="62"/>
+      <c r="X15" s="62"/>
+      <c r="Y15" s="62"/>
+      <c r="Z15" s="62"/>
+      <c r="AA15" s="62"/>
+      <c r="AB15" s="62"/>
+      <c r="AC15" s="62"/>
+      <c r="AD15" s="62"/>
+      <c r="AE15" s="62"/>
+      <c r="AF15" s="62"/>
+      <c r="AG15" s="62"/>
+      <c r="AH15" s="62"/>
+      <c r="AI15" s="62"/>
+      <c r="AJ15" s="62"/>
+      <c r="AK15" s="62"/>
+      <c r="AL15" s="62"/>
     </row>
     <row r="16" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
@@ -1673,14 +1673,14 @@
     </row>
     <row r="17" spans="1:38" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="63" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
       <c r="E17" s="16"/>
       <c r="F17" s="16"/>
-      <c r="G17" s="31" t="s">
+      <c r="G17" s="63" t="s">
         <v>43</v>
       </c>
       <c r="H17" s="16"/>
@@ -1757,14 +1757,14 @@
     </row>
     <row r="19" spans="1:38" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="63" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="16"/>
-      <c r="G19" s="31" t="s">
+      <c r="G19" s="63" t="s">
         <v>18</v>
       </c>
       <c r="H19" s="16"/>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="21" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="64" t="s">
         <v>19</v>
       </c>
       <c r="C21" s="19"/>
@@ -1888,7 +1888,7 @@
       <c r="AH21" s="19"/>
       <c r="AI21" s="19"/>
       <c r="AJ21" s="19"/>
-      <c r="AK21" s="33"/>
+      <c r="AK21" s="65"/>
       <c r="AL21" s="1"/>
     </row>
     <row r="22" spans="1:38" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2396,23 +2396,23 @@
       <c r="P33" s="8"/>
       <c r="Q33" s="8"/>
       <c r="R33" s="1"/>
-      <c r="S33" s="34" t="s">
+      <c r="S33" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="T33" s="26"/>
-      <c r="U33" s="26"/>
-      <c r="V33" s="26"/>
-      <c r="W33" s="26"/>
-      <c r="X33" s="26"/>
-      <c r="Y33" s="26"/>
-      <c r="Z33" s="26"/>
-      <c r="AA33" s="26"/>
-      <c r="AB33" s="26"/>
-      <c r="AC33" s="26"/>
-      <c r="AD33" s="26"/>
-      <c r="AE33" s="26"/>
-      <c r="AF33" s="26"/>
-      <c r="AG33" s="26"/>
+      <c r="T33" s="67"/>
+      <c r="U33" s="67"/>
+      <c r="V33" s="67"/>
+      <c r="W33" s="67"/>
+      <c r="X33" s="67"/>
+      <c r="Y33" s="67"/>
+      <c r="Z33" s="67"/>
+      <c r="AA33" s="67"/>
+      <c r="AB33" s="67"/>
+      <c r="AC33" s="67"/>
+      <c r="AD33" s="67"/>
+      <c r="AE33" s="67"/>
+      <c r="AF33" s="67"/>
+      <c r="AG33" s="67"/>
       <c r="AH33" s="1"/>
       <c r="AI33" s="1"/>
       <c r="AJ33" s="1"/>
@@ -2429,34 +2429,34 @@
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
       <c r="I34" s="9"/>
-      <c r="J34" s="35" t="s">
+      <c r="J34" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="K34" s="36"/>
-      <c r="L34" s="36"/>
-      <c r="M34" s="36"/>
-      <c r="N34" s="36"/>
-      <c r="O34" s="36"/>
-      <c r="P34" s="36"/>
-      <c r="Q34" s="36"/>
+      <c r="K34" s="69"/>
+      <c r="L34" s="69"/>
+      <c r="M34" s="69"/>
+      <c r="N34" s="69"/>
+      <c r="O34" s="69"/>
+      <c r="P34" s="69"/>
+      <c r="Q34" s="69"/>
       <c r="R34" s="9"/>
-      <c r="S34" s="35" t="s">
+      <c r="S34" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="T34" s="36"/>
-      <c r="U34" s="36"/>
-      <c r="V34" s="36"/>
-      <c r="W34" s="36"/>
-      <c r="X34" s="36"/>
-      <c r="Y34" s="36"/>
-      <c r="Z34" s="36"/>
-      <c r="AA34" s="36"/>
-      <c r="AB34" s="36"/>
-      <c r="AC34" s="36"/>
-      <c r="AD34" s="36"/>
-      <c r="AE34" s="36"/>
-      <c r="AF34" s="36"/>
-      <c r="AG34" s="36"/>
+      <c r="T34" s="69"/>
+      <c r="U34" s="69"/>
+      <c r="V34" s="69"/>
+      <c r="W34" s="69"/>
+      <c r="X34" s="69"/>
+      <c r="Y34" s="69"/>
+      <c r="Z34" s="69"/>
+      <c r="AA34" s="69"/>
+      <c r="AB34" s="69"/>
+      <c r="AC34" s="69"/>
+      <c r="AD34" s="69"/>
+      <c r="AE34" s="69"/>
+      <c r="AF34" s="69"/>
+      <c r="AG34" s="69"/>
       <c r="AH34" s="1"/>
       <c r="AI34" s="1"/>
       <c r="AJ34" s="1"/>
@@ -2524,21 +2524,21 @@
       <c r="P36" s="8"/>
       <c r="Q36" s="8"/>
       <c r="R36" s="1"/>
-      <c r="S36" s="34"/>
-      <c r="T36" s="26"/>
-      <c r="U36" s="26"/>
-      <c r="V36" s="26"/>
-      <c r="W36" s="26"/>
-      <c r="X36" s="26"/>
-      <c r="Y36" s="26"/>
-      <c r="Z36" s="26"/>
-      <c r="AA36" s="26"/>
-      <c r="AB36" s="26"/>
-      <c r="AC36" s="26"/>
-      <c r="AD36" s="26"/>
-      <c r="AE36" s="26"/>
-      <c r="AF36" s="26"/>
-      <c r="AG36" s="26"/>
+      <c r="S36" s="66"/>
+      <c r="T36" s="67"/>
+      <c r="U36" s="67"/>
+      <c r="V36" s="67"/>
+      <c r="W36" s="67"/>
+      <c r="X36" s="67"/>
+      <c r="Y36" s="67"/>
+      <c r="Z36" s="67"/>
+      <c r="AA36" s="67"/>
+      <c r="AB36" s="67"/>
+      <c r="AC36" s="67"/>
+      <c r="AD36" s="67"/>
+      <c r="AE36" s="67"/>
+      <c r="AF36" s="67"/>
+      <c r="AG36" s="67"/>
       <c r="AH36" s="1"/>
       <c r="AI36" s="1"/>
       <c r="AJ36" s="1"/>
@@ -2555,34 +2555,34 @@
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
-      <c r="J37" s="35" t="s">
+      <c r="J37" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="K37" s="36"/>
-      <c r="L37" s="36"/>
-      <c r="M37" s="36"/>
-      <c r="N37" s="36"/>
-      <c r="O37" s="36"/>
-      <c r="P37" s="36"/>
-      <c r="Q37" s="36"/>
+      <c r="K37" s="69"/>
+      <c r="L37" s="69"/>
+      <c r="M37" s="69"/>
+      <c r="N37" s="69"/>
+      <c r="O37" s="69"/>
+      <c r="P37" s="69"/>
+      <c r="Q37" s="69"/>
       <c r="R37" s="9"/>
-      <c r="S37" s="35" t="s">
+      <c r="S37" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="T37" s="36"/>
-      <c r="U37" s="36"/>
-      <c r="V37" s="36"/>
-      <c r="W37" s="36"/>
-      <c r="X37" s="36"/>
-      <c r="Y37" s="36"/>
-      <c r="Z37" s="36"/>
-      <c r="AA37" s="36"/>
-      <c r="AB37" s="36"/>
-      <c r="AC37" s="36"/>
-      <c r="AD37" s="36"/>
-      <c r="AE37" s="36"/>
-      <c r="AF37" s="36"/>
-      <c r="AG37" s="36"/>
+      <c r="T37" s="69"/>
+      <c r="U37" s="69"/>
+      <c r="V37" s="69"/>
+      <c r="W37" s="69"/>
+      <c r="X37" s="69"/>
+      <c r="Y37" s="69"/>
+      <c r="Z37" s="69"/>
+      <c r="AA37" s="69"/>
+      <c r="AB37" s="69"/>
+      <c r="AC37" s="69"/>
+      <c r="AD37" s="69"/>
+      <c r="AE37" s="69"/>
+      <c r="AF37" s="69"/>
+      <c r="AG37" s="69"/>
       <c r="AH37" s="1"/>
       <c r="AI37" s="1"/>
       <c r="AJ37" s="1"/>
